--- a/Turnazione_Personale_2026-2027.xlsx
+++ b/Turnazione_Personale_2026-2027.xlsx
@@ -3077,9 +3077,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
@@ -3087,9 +3087,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -3127,9 +3127,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="P5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="Q5" s="13" t="inlineStr">
@@ -3137,9 +3137,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S5" s="13" t="inlineStr">
@@ -3177,9 +3177,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Z5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AA5" s="13" t="inlineStr">
@@ -3187,9 +3187,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AB5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="AB5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AC5" s="13" t="inlineStr">
@@ -3227,9 +3227,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AJ5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="AJ5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AK5" s="13" t="inlineStr">
@@ -3237,9 +3237,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AL5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="AL5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AM5" s="13" t="inlineStr">
@@ -3277,9 +3277,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AT5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="AT5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AU5" s="13" t="inlineStr">
@@ -3287,9 +3287,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AV5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="AV5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AW5" s="13" t="inlineStr">
@@ -3327,9 +3327,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BD5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BD5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BE5" s="13" t="inlineStr">
@@ -3337,9 +3337,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BF5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BF5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BG5" s="13" t="inlineStr">
@@ -3377,9 +3377,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BN5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BN5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BO5" s="13" t="inlineStr">
@@ -3387,9 +3387,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BP5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BP5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BQ5" s="13" t="inlineStr">
@@ -3422,9 +3422,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BW5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BW5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BX5" s="13" t="inlineStr">
@@ -3432,9 +3432,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BY5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BY5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BZ5" s="13" t="inlineStr">
@@ -3467,9 +3467,9 @@
           <t xml:space="preserve">X</t>
         </is>
       </c>
-      <c r="CF5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CF5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="CG5" s="13" t="inlineStr">
@@ -3477,9 +3477,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CH5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CH5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="CI5" s="13" t="inlineStr">
@@ -3507,9 +3507,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CN5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CN5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="CO5" s="13" t="inlineStr">
@@ -3517,9 +3517,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CP5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CP5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="CQ5" s="13" t="inlineStr">
@@ -3557,9 +3557,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CX5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CX5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="CY5" s="13" t="inlineStr">
@@ -3567,9 +3567,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CZ5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CZ5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="DA5" s="13" t="inlineStr">
@@ -3607,9 +3607,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DH5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="DH5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="DI5" s="13" t="inlineStr">
@@ -3617,9 +3617,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DJ5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="DJ5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="DK5" s="13" t="inlineStr">
@@ -3657,9 +3657,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DR5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="DR5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="DS5" s="13" t="inlineStr">
@@ -3667,9 +3667,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DT5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="DT5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="DU5" s="13" t="inlineStr">
@@ -3707,9 +3707,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EB5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="EB5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EC5" s="13" t="inlineStr">
@@ -3717,9 +3717,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="ED5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="ED5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EE5" s="13" t="inlineStr">
@@ -3757,9 +3757,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EL5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="EL5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EM5" s="13" t="inlineStr">
@@ -3767,9 +3767,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EN5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="EN5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EO5" s="13" t="inlineStr">
@@ -3802,9 +3802,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EU5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="EU5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EV5" s="13" t="inlineStr">
@@ -3812,9 +3812,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EW5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="EW5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EX5" s="13" t="inlineStr">
@@ -3852,9 +3852,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FE5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FE5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="FF5" s="13" t="inlineStr">
@@ -3862,9 +3862,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FG5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FG5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="FH5" s="13" t="inlineStr">
@@ -3902,9 +3902,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FO5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FO5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="FP5" s="13" t="inlineStr">
@@ -3912,9 +3912,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FQ5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FQ5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="FR5" s="13" t="inlineStr">
@@ -3947,9 +3947,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FX5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FX5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="FY5" s="13" t="inlineStr">
@@ -3957,9 +3957,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FZ5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FZ5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GA5" s="13" t="inlineStr">
@@ -3997,9 +3997,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GH5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="GH5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="GI5" s="13" t="inlineStr">
@@ -4042,9 +4042,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GQ5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="GQ5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="GR5" s="13" t="inlineStr">
@@ -4052,9 +4052,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GS5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="GS5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GT5" s="13" t="inlineStr">
@@ -4092,9 +4092,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HA5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HA5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HB5" s="13" t="inlineStr">
@@ -4102,9 +4102,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HC5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HC5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HD5" s="13" t="inlineStr">
@@ -4142,9 +4142,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HK5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HK5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HL5" s="13" t="inlineStr">
@@ -4152,9 +4152,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HM5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HM5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HN5" s="13" t="inlineStr">
@@ -4192,9 +4192,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HU5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HU5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HV5" s="13" t="inlineStr">
@@ -4202,9 +4202,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HW5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HW5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HX5" s="13" t="inlineStr">
@@ -4242,9 +4242,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IE5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="IE5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="IF5" s="13" t="inlineStr">
@@ -4252,9 +4252,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IG5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="IG5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="IH5" s="13" t="inlineStr">
@@ -4292,9 +4292,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IO5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="IO5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="IP5" s="13" t="inlineStr">
@@ -4302,9 +4302,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IQ5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="IQ5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="IR5" s="13" t="inlineStr">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="IV5" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -6917,9 +6917,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -6927,9 +6927,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -6967,9 +6967,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" s="13" t="inlineStr">
@@ -6977,9 +6977,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="S8" s="13" t="inlineStr">
@@ -7017,9 +7017,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="Z8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AA8" s="13" t="inlineStr">
@@ -7027,9 +7027,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AB8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AC8" s="13" t="inlineStr">
@@ -7067,9 +7067,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AJ8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="AJ8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AK8" s="13" t="inlineStr">
@@ -7077,9 +7077,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AL8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="AL8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AM8" s="13" t="inlineStr">
@@ -7117,9 +7117,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AT8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="AT8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="AU8" s="13" t="inlineStr">
@@ -7127,9 +7127,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="AV8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="AV8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="AW8" s="13" t="inlineStr">
@@ -7167,9 +7167,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BD8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BD8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BE8" s="13" t="inlineStr">
@@ -7177,9 +7177,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BF8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BF8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BG8" s="13" t="inlineStr">
@@ -7217,9 +7217,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BN8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BN8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BO8" s="13" t="inlineStr">
@@ -7227,9 +7227,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BP8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BP8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BQ8" s="13" t="inlineStr">
@@ -7262,9 +7262,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BW8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="BW8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="BX8" s="13" t="inlineStr">
@@ -7272,9 +7272,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="BY8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="BY8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="BZ8" s="13" t="inlineStr">
@@ -7307,9 +7307,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CF8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CF8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="CG8" s="13" t="inlineStr">
@@ -7317,9 +7317,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CH8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CH8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="CI8" s="13" t="inlineStr">
@@ -7347,9 +7347,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CN8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CN8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="CO8" s="13" t="inlineStr">
@@ -7357,9 +7357,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CP8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CP8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="CQ8" s="13" t="inlineStr">
@@ -7397,9 +7397,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CX8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="CX8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="CY8" s="13" t="inlineStr">
@@ -7407,9 +7407,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="CZ8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="CZ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="DA8" s="13" t="inlineStr">
@@ -7447,9 +7447,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DH8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="DH8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="DI8" s="13" t="inlineStr">
@@ -7457,9 +7457,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DJ8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="DJ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="DK8" s="13" t="inlineStr">
@@ -7497,9 +7497,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DR8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="DR8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="DS8" s="13" t="inlineStr">
@@ -7507,9 +7507,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="DT8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="DT8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="DU8" s="13" t="inlineStr">
@@ -7547,9 +7547,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EB8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="EB8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EC8" s="13" t="inlineStr">
@@ -7557,9 +7557,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="ED8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="ED8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EE8" s="13" t="inlineStr">
@@ -7597,9 +7597,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EL8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="EL8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EM8" s="13" t="inlineStr">
@@ -7607,9 +7607,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EN8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="EN8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EO8" s="13" t="inlineStr">
@@ -7642,9 +7642,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EU8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="EU8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="EV8" s="13" t="inlineStr">
@@ -7652,9 +7652,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="EW8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="EW8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="EX8" s="13" t="inlineStr">
@@ -7692,9 +7692,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FE8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FE8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="FF8" s="13" t="inlineStr">
@@ -7702,9 +7702,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FG8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FG8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="FH8" s="13" t="inlineStr">
@@ -7742,9 +7742,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FO8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FO8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="FP8" s="13" t="inlineStr">
@@ -7752,9 +7752,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FQ8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FQ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="FR8" s="13" t="inlineStr">
@@ -7787,9 +7787,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FX8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="FX8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="FY8" s="13" t="inlineStr">
@@ -7797,9 +7797,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="FZ8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="FZ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="GA8" s="13" t="inlineStr">
@@ -7837,9 +7837,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GH8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="GH8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GI8" s="13" t="inlineStr">
@@ -7882,9 +7882,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GQ8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="GQ8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GR8" s="13" t="inlineStr">
@@ -7892,9 +7892,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="GS8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="GS8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="GT8" s="13" t="inlineStr">
@@ -7932,9 +7932,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HA8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HA8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HB8" s="13" t="inlineStr">
@@ -7942,9 +7942,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HC8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HC8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HD8" s="13" t="inlineStr">
@@ -7982,9 +7982,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HK8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HK8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HL8" s="13" t="inlineStr">
@@ -7992,9 +7992,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HM8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HM8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HN8" s="13" t="inlineStr">
@@ -8032,9 +8032,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HU8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="HU8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="HV8" s="13" t="inlineStr">
@@ -8042,9 +8042,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="HW8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="HW8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="HX8" s="13" t="inlineStr">
@@ -8082,9 +8082,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IE8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="IE8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="IF8" s="13" t="inlineStr">
@@ -8092,9 +8092,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IG8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="IG8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="IH8" s="13" t="inlineStr">
@@ -8132,9 +8132,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IO8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X</t>
+      <c r="IO8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="IP8" s="13" t="inlineStr">
@@ -8142,9 +8142,9 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="IQ8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="IQ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="IR8" s="13" t="inlineStr">
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="IV8" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -16227,12 +16227,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/09/2026</t>
+          <t xml:space="preserve">07/09/2026</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F5" s="9">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/09/2026</t>
+          <t xml:space="preserve">21/09/2026</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F8" s="9">
@@ -16395,12 +16395,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/10/2026</t>
+          <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F11" s="9">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/10/2026</t>
+          <t xml:space="preserve">19/10/2026</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F14" s="9">
@@ -16563,12 +16563,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/11/2026</t>
+          <t xml:space="preserve">02/11/2026</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F17" s="9">
@@ -16647,12 +16647,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/11/2026</t>
+          <t xml:space="preserve">16/11/2026</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F20" s="9">
@@ -16731,12 +16731,12 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/12/2026</t>
+          <t xml:space="preserve">30/11/2026</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F23" s="9">
@@ -16815,12 +16815,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/12/2026</t>
+          <t xml:space="preserve">14/12/2026</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F26" s="9">
@@ -16899,12 +16899,12 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/12/2026</t>
+          <t xml:space="preserve">28/12/2026</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F29" s="9">
@@ -16955,12 +16955,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/01/2027</t>
+          <t xml:space="preserve">11/01/2027</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F31" s="9">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/01/2027</t>
+          <t xml:space="preserve">25/01/2027</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F34" s="9">
@@ -17123,12 +17123,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/02/2027</t>
+          <t xml:space="preserve">08/02/2027</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F37" s="9">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/02/2027</t>
+          <t xml:space="preserve">22/02/2027</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F40" s="9">
@@ -17291,12 +17291,12 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/03/2027</t>
+          <t xml:space="preserve">08/03/2027</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F43" s="9">
@@ -17375,12 +17375,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/03/2027</t>
+          <t xml:space="preserve">22/03/2027</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F46" s="9">
@@ -17459,12 +17459,12 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/04/2027</t>
+          <t xml:space="preserve">05/04/2027</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F49" s="9">
@@ -17543,12 +17543,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/04/2027</t>
+          <t xml:space="preserve">19/04/2027</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F52" s="9">
@@ -17627,12 +17627,12 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/05/2027</t>
+          <t xml:space="preserve">03/05/2027</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F55" s="9">
@@ -17711,12 +17711,12 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/05/2027</t>
+          <t xml:space="preserve">17/05/2027</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F58" s="9">
@@ -17795,16 +17795,16 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/06/2027</t>
+          <t xml:space="preserve">31/05/2027</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F61" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -17823,16 +17823,16 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/06/2027</t>
+          <t xml:space="preserve">04/06/2027</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F62" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -17851,16 +17851,16 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/06/2027</t>
+          <t xml:space="preserve">10/06/2027</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -17879,12 +17879,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/06/2027</t>
+          <t xml:space="preserve">14/06/2027</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F64" s="9">
@@ -17907,16 +17907,16 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/06/2027</t>
+          <t xml:space="preserve">18/06/2027</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -17935,16 +17935,16 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/06/2027</t>
+          <t xml:space="preserve">24/06/2027</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -17963,12 +17963,12 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/07/2027</t>
+          <t xml:space="preserve">28/06/2027</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F67" s="9">
@@ -17991,16 +17991,16 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/07/2027</t>
+          <t xml:space="preserve">02/07/2027</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F68" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -18019,16 +18019,16 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/07/2027</t>
+          <t xml:space="preserve">08/07/2027</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -18047,12 +18047,12 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/07/2027</t>
+          <t xml:space="preserve">12/07/2027</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F70" s="9">
@@ -18075,16 +18075,16 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/07/2027</t>
+          <t xml:space="preserve">16/07/2027</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F71" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -18103,16 +18103,16 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/07/2027</t>
+          <t xml:space="preserve">22/07/2027</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -18131,12 +18131,12 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/07/2027</t>
+          <t xml:space="preserve">26/07/2027</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F73" s="9">
@@ -18159,16 +18159,16 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/08/2027</t>
+          <t xml:space="preserve">30/07/2027</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F74" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -18187,16 +18187,16 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/08/2027</t>
+          <t xml:space="preserve">05/08/2027</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -18215,12 +18215,12 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/08/2027</t>
+          <t xml:space="preserve">09/08/2027</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F76" s="9">
@@ -18243,16 +18243,16 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/08/2027</t>
+          <t xml:space="preserve">13/08/2027</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F77" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -18271,16 +18271,16 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/08/2027</t>
+          <t xml:space="preserve">19/08/2027</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F78" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -18299,12 +18299,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/08/2027</t>
+          <t xml:space="preserve">23/08/2027</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F79" s="9">
@@ -18319,20 +18319,20 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prota</t>
+          <t xml:space="preserve">Caforio</t>
         </is>
       </c>
       <c r="C80" s="9">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/09/2026</t>
+          <t xml:space="preserve">27/08/2027</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F80" s="9">
@@ -18351,16 +18351,16 @@
         </is>
       </c>
       <c r="C81" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/09/2026</t>
+          <t xml:space="preserve">02/09/2026</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F81" s="9">
@@ -18379,20 +18379,20 @@
         </is>
       </c>
       <c r="C82" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/09/2026</t>
+          <t xml:space="preserve">04/09/2026</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F82" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -18407,20 +18407,20 @@
         </is>
       </c>
       <c r="C83" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/09/2026</t>
+          <t xml:space="preserve">08/09/2026</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F83" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -18435,16 +18435,16 @@
         </is>
       </c>
       <c r="C84" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/09/2026</t>
+          <t xml:space="preserve">14/09/2026</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F84" s="9">
@@ -18463,20 +18463,20 @@
         </is>
       </c>
       <c r="C85" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/09/2026</t>
+          <t xml:space="preserve">16/09/2026</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F85" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -18491,20 +18491,20 @@
         </is>
       </c>
       <c r="C86" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/09/2026</t>
+          <t xml:space="preserve">22/09/2026</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F86" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -18519,16 +18519,16 @@
         </is>
       </c>
       <c r="C87" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">28/09/2026</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F87" s="9">
@@ -18547,20 +18547,20 @@
         </is>
       </c>
       <c r="C88" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">06/10/2026</t>
+          <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F88" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -18575,20 +18575,20 @@
         </is>
       </c>
       <c r="C89" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">06/10/2026</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F89" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -18603,16 +18603,16 @@
         </is>
       </c>
       <c r="C90" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/10/2026</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F90" s="9">
@@ -18631,20 +18631,20 @@
         </is>
       </c>
       <c r="C91" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/10/2026</t>
+          <t xml:space="preserve">14/10/2026</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F91" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -18659,20 +18659,20 @@
         </is>
       </c>
       <c r="C92" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/10/2026</t>
+          <t xml:space="preserve">20/10/2026</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F92" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -18687,16 +18687,16 @@
         </is>
       </c>
       <c r="C93" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/10/2026</t>
+          <t xml:space="preserve">26/10/2026</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F93" s="9">
@@ -18715,20 +18715,20 @@
         </is>
       </c>
       <c r="C94" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/11/2026</t>
+          <t xml:space="preserve">28/10/2026</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F94" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -18743,20 +18743,20 @@
         </is>
       </c>
       <c r="C95" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/11/2026</t>
+          <t xml:space="preserve">03/11/2026</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -18771,16 +18771,16 @@
         </is>
       </c>
       <c r="C96" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/11/2026</t>
+          <t xml:space="preserve">09/11/2026</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F96" s="9">
@@ -18799,20 +18799,20 @@
         </is>
       </c>
       <c r="C97" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/11/2026</t>
+          <t xml:space="preserve">11/11/2026</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F97" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -18827,20 +18827,20 @@
         </is>
       </c>
       <c r="C98" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/11/2026</t>
+          <t xml:space="preserve">17/11/2026</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F98" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -18855,16 +18855,16 @@
         </is>
       </c>
       <c r="C99" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/11/2026</t>
+          <t xml:space="preserve">23/11/2026</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F99" s="9">
@@ -18883,20 +18883,20 @@
         </is>
       </c>
       <c r="C100" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/12/2026</t>
+          <t xml:space="preserve">25/11/2026</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F100" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -18911,20 +18911,20 @@
         </is>
       </c>
       <c r="C101" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/12/2026</t>
+          <t xml:space="preserve">01/12/2026</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F101" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -18939,16 +18939,16 @@
         </is>
       </c>
       <c r="C102" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">07/12/2026</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F102" s="9">
@@ -18967,20 +18967,20 @@
         </is>
       </c>
       <c r="C103" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/12/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F103" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -18995,20 +18995,20 @@
         </is>
       </c>
       <c r="C104" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/12/2026</t>
+          <t xml:space="preserve">15/12/2026</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F104" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -19023,16 +19023,16 @@
         </is>
       </c>
       <c r="C105" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/12/2026</t>
+          <t xml:space="preserve">21/12/2026</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F105" s="9">
@@ -19051,20 +19051,20 @@
         </is>
       </c>
       <c r="C106" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/12/2026</t>
+          <t xml:space="preserve">23/12/2026</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F106" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -19079,20 +19079,20 @@
         </is>
       </c>
       <c r="C107" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/01/2027</t>
+          <t xml:space="preserve">29/12/2026</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F107" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -19107,16 +19107,16 @@
         </is>
       </c>
       <c r="C108" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/01/2027</t>
+          <t xml:space="preserve">04/01/2027</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F108" s="9">
@@ -19135,20 +19135,20 @@
         </is>
       </c>
       <c r="C109" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/01/2027</t>
+          <t xml:space="preserve">08/01/2027</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F109" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -19163,20 +19163,20 @@
         </is>
       </c>
       <c r="C110" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/01/2027</t>
+          <t xml:space="preserve">12/01/2027</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F110" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -19191,16 +19191,16 @@
         </is>
       </c>
       <c r="C111" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/01/2027</t>
+          <t xml:space="preserve">18/01/2027</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F111" s="9">
@@ -19219,20 +19219,20 @@
         </is>
       </c>
       <c r="C112" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/01/2027</t>
+          <t xml:space="preserve">20/01/2027</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F112" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -19247,20 +19247,20 @@
         </is>
       </c>
       <c r="C113" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/02/2027</t>
+          <t xml:space="preserve">26/01/2027</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F113" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -19275,16 +19275,16 @@
         </is>
       </c>
       <c r="C114" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/02/2027</t>
+          <t xml:space="preserve">01/02/2027</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F114" s="9">
@@ -19303,20 +19303,20 @@
         </is>
       </c>
       <c r="C115" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/02/2027</t>
+          <t xml:space="preserve">03/02/2027</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F115" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -19331,20 +19331,20 @@
         </is>
       </c>
       <c r="C116" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/02/2027</t>
+          <t xml:space="preserve">09/02/2027</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F116" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -19359,16 +19359,16 @@
         </is>
       </c>
       <c r="C117" s="9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/02/2027</t>
+          <t xml:space="preserve">15/02/2027</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F117" s="9">
@@ -19387,20 +19387,20 @@
         </is>
       </c>
       <c r="C118" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/02/2027</t>
+          <t xml:space="preserve">17/02/2027</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F118" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -19415,20 +19415,20 @@
         </is>
       </c>
       <c r="C119" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/03/2027</t>
+          <t xml:space="preserve">23/02/2027</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F119" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -19443,16 +19443,16 @@
         </is>
       </c>
       <c r="C120" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/03/2027</t>
+          <t xml:space="preserve">01/03/2027</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F120" s="9">
@@ -19471,20 +19471,20 @@
         </is>
       </c>
       <c r="C121" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/03/2027</t>
+          <t xml:space="preserve">03/03/2027</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F121" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -19499,20 +19499,20 @@
         </is>
       </c>
       <c r="C122" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/03/2027</t>
+          <t xml:space="preserve">09/03/2027</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F122" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -19527,16 +19527,16 @@
         </is>
       </c>
       <c r="C123" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/03/2027</t>
+          <t xml:space="preserve">15/03/2027</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F123" s="9">
@@ -19555,20 +19555,20 @@
         </is>
       </c>
       <c r="C124" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/03/2027</t>
+          <t xml:space="preserve">17/03/2027</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F124" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -19583,20 +19583,20 @@
         </is>
       </c>
       <c r="C125" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31/03/2027</t>
+          <t xml:space="preserve">23/03/2027</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F125" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -19611,16 +19611,16 @@
         </is>
       </c>
       <c r="C126" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/04/2027</t>
+          <t xml:space="preserve">31/03/2027</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F126" s="9">
@@ -19639,20 +19639,20 @@
         </is>
       </c>
       <c r="C127" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">06/04/2027</t>
+          <t xml:space="preserve">02/04/2027</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F127" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -19667,20 +19667,20 @@
         </is>
       </c>
       <c r="C128" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/04/2027</t>
+          <t xml:space="preserve">06/04/2027</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F128" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -19695,16 +19695,16 @@
         </is>
       </c>
       <c r="C129" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/04/2027</t>
+          <t xml:space="preserve">12/04/2027</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F129" s="9">
@@ -19723,20 +19723,20 @@
         </is>
       </c>
       <c r="C130" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/04/2027</t>
+          <t xml:space="preserve">14/04/2027</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F130" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -19751,20 +19751,20 @@
         </is>
       </c>
       <c r="C131" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/04/2027</t>
+          <t xml:space="preserve">20/04/2027</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -19779,16 +19779,16 @@
         </is>
       </c>
       <c r="C132" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/04/2027</t>
+          <t xml:space="preserve">26/04/2027</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F132" s="9">
@@ -19807,20 +19807,20 @@
         </is>
       </c>
       <c r="C133" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/05/2027</t>
+          <t xml:space="preserve">28/04/2027</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F133" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -19835,20 +19835,20 @@
         </is>
       </c>
       <c r="C134" s="9">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/05/2027</t>
+          <t xml:space="preserve">04/05/2027</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F134" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -19863,16 +19863,16 @@
         </is>
       </c>
       <c r="C135" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/05/2027</t>
+          <t xml:space="preserve">12/05/2027</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F135" s="9">
@@ -19891,20 +19891,20 @@
         </is>
       </c>
       <c r="C136" s="9">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/05/2027</t>
+          <t xml:space="preserve">14/05/2027</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F136" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -19919,20 +19919,20 @@
         </is>
       </c>
       <c r="C137" s="9">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/05/2027</t>
+          <t xml:space="preserve">18/05/2027</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F137" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -19947,16 +19947,16 @@
         </is>
       </c>
       <c r="C138" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/05/2027</t>
+          <t xml:space="preserve">24/05/2027</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F138" s="9">
@@ -19975,20 +19975,20 @@
         </is>
       </c>
       <c r="C139" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/06/2027</t>
+          <t xml:space="preserve">26/05/2027</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F139" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -20003,20 +20003,20 @@
         </is>
       </c>
       <c r="C140" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/06/2027</t>
+          <t xml:space="preserve">01/06/2027</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F140" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -20031,16 +20031,16 @@
         </is>
       </c>
       <c r="C141" s="9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/06/2027</t>
+          <t xml:space="preserve">07/06/2027</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F141" s="9">
@@ -20059,20 +20059,20 @@
         </is>
       </c>
       <c r="C142" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/06/2027</t>
+          <t xml:space="preserve">09/06/2027</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F142" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -20087,20 +20087,20 @@
         </is>
       </c>
       <c r="C143" s="9">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/06/2027</t>
+          <t xml:space="preserve">15/06/2027</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F143" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -20115,16 +20115,16 @@
         </is>
       </c>
       <c r="C144" s="9">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/06/2027</t>
+          <t xml:space="preserve">21/06/2027</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F144" s="9">
@@ -20143,20 +20143,20 @@
         </is>
       </c>
       <c r="C145" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/06/2027</t>
+          <t xml:space="preserve">23/06/2027</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F145" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -20171,20 +20171,20 @@
         </is>
       </c>
       <c r="C146" s="9">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/07/2027</t>
+          <t xml:space="preserve">29/06/2027</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F146" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -20199,16 +20199,16 @@
         </is>
       </c>
       <c r="C147" s="9">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/07/2027</t>
+          <t xml:space="preserve">05/07/2027</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F147" s="9">
@@ -20227,20 +20227,20 @@
         </is>
       </c>
       <c r="C148" s="9">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/07/2027</t>
+          <t xml:space="preserve">07/07/2027</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F148" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -20255,20 +20255,20 @@
         </is>
       </c>
       <c r="C149" s="9">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/07/2027</t>
+          <t xml:space="preserve">13/07/2027</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F149" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -20283,16 +20283,16 @@
         </is>
       </c>
       <c r="C150" s="9">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/07/2027</t>
+          <t xml:space="preserve">19/07/2027</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F150" s="9">
@@ -20311,20 +20311,20 @@
         </is>
       </c>
       <c r="C151" s="9">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/07/2027</t>
+          <t xml:space="preserve">21/07/2027</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F151" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -20339,20 +20339,20 @@
         </is>
       </c>
       <c r="C152" s="9">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/08/2027</t>
+          <t xml:space="preserve">27/07/2027</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F152" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -20367,16 +20367,16 @@
         </is>
       </c>
       <c r="C153" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/08/2027</t>
+          <t xml:space="preserve">02/08/2027</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F153" s="9">
@@ -20395,20 +20395,20 @@
         </is>
       </c>
       <c r="C154" s="9">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/08/2027</t>
+          <t xml:space="preserve">04/08/2027</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F154" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -20423,20 +20423,20 @@
         </is>
       </c>
       <c r="C155" s="9">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/08/2027</t>
+          <t xml:space="preserve">10/08/2027</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F155" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -20451,16 +20451,16 @@
         </is>
       </c>
       <c r="C156" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/08/2027</t>
+          <t xml:space="preserve">16/08/2027</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F156" s="9">
@@ -20479,20 +20479,20 @@
         </is>
       </c>
       <c r="C157" s="9">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/08/2027</t>
+          <t xml:space="preserve">18/08/2027</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F157" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -20507,16 +20507,16 @@
         </is>
       </c>
       <c r="C158" s="9">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/08/2027</t>
+          <t xml:space="preserve">24/08/2027</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F158" s="9">
@@ -20531,24 +20531,24 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amenduni</t>
+          <t xml:space="preserve">Prota</t>
         </is>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/09/2026</t>
+          <t xml:space="preserve">30/08/2027</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F159" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -20563,16 +20563,16 @@
         </is>
       </c>
       <c r="C160" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/09/2026</t>
+          <t xml:space="preserve">02/09/2026</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F160" s="9">
@@ -20591,16 +20591,16 @@
         </is>
       </c>
       <c r="C161" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/09/2026</t>
+          <t xml:space="preserve">04/09/2026</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F161" s="9">
@@ -20619,16 +20619,16 @@
         </is>
       </c>
       <c r="C162" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/09/2026</t>
+          <t xml:space="preserve">07/09/2026</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F162" s="9">
@@ -20647,16 +20647,16 @@
         </is>
       </c>
       <c r="C163" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/09/2026</t>
+          <t xml:space="preserve">09/09/2026</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F163" s="9">
@@ -20675,16 +20675,16 @@
         </is>
       </c>
       <c r="C164" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/09/2026</t>
+          <t xml:space="preserve">14/09/2026</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F164" s="9">
@@ -20703,16 +20703,16 @@
         </is>
       </c>
       <c r="C165" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/09/2026</t>
+          <t xml:space="preserve">16/09/2026</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F165" s="9">
@@ -20731,16 +20731,16 @@
         </is>
       </c>
       <c r="C166" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/09/2026</t>
+          <t xml:space="preserve">21/09/2026</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F166" s="9">
@@ -20759,16 +20759,16 @@
         </is>
       </c>
       <c r="C167" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/09/2026</t>
+          <t xml:space="preserve">23/09/2026</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F167" s="9">
@@ -20787,16 +20787,16 @@
         </is>
       </c>
       <c r="C168" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">28/09/2026</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F168" s="9">
@@ -20815,16 +20815,16 @@
         </is>
       </c>
       <c r="C169" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/10/2026</t>
+          <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F169" s="9">
@@ -20843,16 +20843,16 @@
         </is>
       </c>
       <c r="C170" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/10/2026</t>
+          <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F170" s="9">
@@ -20871,16 +20871,16 @@
         </is>
       </c>
       <c r="C171" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/10/2026</t>
+          <t xml:space="preserve">07/10/2026</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F171" s="9">
@@ -20899,16 +20899,16 @@
         </is>
       </c>
       <c r="C172" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/10/2026</t>
+          <t xml:space="preserve">12/10/2026</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F172" s="9">
@@ -20927,16 +20927,16 @@
         </is>
       </c>
       <c r="C173" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/10/2026</t>
+          <t xml:space="preserve">14/10/2026</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F173" s="9">
@@ -20955,16 +20955,16 @@
         </is>
       </c>
       <c r="C174" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/10/2026</t>
+          <t xml:space="preserve">19/10/2026</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F174" s="9">
@@ -20983,16 +20983,16 @@
         </is>
       </c>
       <c r="C175" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/10/2026</t>
+          <t xml:space="preserve">21/10/2026</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F175" s="9">
@@ -21011,16 +21011,16 @@
         </is>
       </c>
       <c r="C176" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/10/2026</t>
+          <t xml:space="preserve">26/10/2026</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F176" s="9">
@@ -21039,16 +21039,16 @@
         </is>
       </c>
       <c r="C177" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/11/2026</t>
+          <t xml:space="preserve">28/10/2026</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F177" s="9">
@@ -21067,16 +21067,16 @@
         </is>
       </c>
       <c r="C178" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/11/2026</t>
+          <t xml:space="preserve">02/11/2026</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F178" s="9">
@@ -21095,16 +21095,16 @@
         </is>
       </c>
       <c r="C179" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/11/2026</t>
+          <t xml:space="preserve">04/11/2026</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F179" s="9">
@@ -21123,16 +21123,16 @@
         </is>
       </c>
       <c r="C180" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/11/2026</t>
+          <t xml:space="preserve">09/11/2026</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F180" s="9">
@@ -21151,16 +21151,16 @@
         </is>
       </c>
       <c r="C181" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/11/2026</t>
+          <t xml:space="preserve">11/11/2026</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F181" s="9">
@@ -21179,16 +21179,16 @@
         </is>
       </c>
       <c r="C182" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/11/2026</t>
+          <t xml:space="preserve">16/11/2026</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F182" s="9">
@@ -21207,16 +21207,16 @@
         </is>
       </c>
       <c r="C183" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/11/2026</t>
+          <t xml:space="preserve">18/11/2026</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F183" s="9">
@@ -21235,16 +21235,16 @@
         </is>
       </c>
       <c r="C184" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/11/2026</t>
+          <t xml:space="preserve">23/11/2026</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F184" s="9">
@@ -21263,16 +21263,16 @@
         </is>
       </c>
       <c r="C185" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/11/2026</t>
+          <t xml:space="preserve">25/11/2026</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F185" s="9">
@@ -21291,16 +21291,16 @@
         </is>
       </c>
       <c r="C186" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/12/2026</t>
+          <t xml:space="preserve">30/11/2026</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F186" s="9">
@@ -21319,16 +21319,16 @@
         </is>
       </c>
       <c r="C187" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/12/2026</t>
+          <t xml:space="preserve">02/12/2026</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F187" s="9">
@@ -21347,16 +21347,16 @@
         </is>
       </c>
       <c r="C188" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">07/12/2026</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F188" s="9">
@@ -21375,16 +21375,16 @@
         </is>
       </c>
       <c r="C189" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/12/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F189" s="9">
@@ -21403,16 +21403,16 @@
         </is>
       </c>
       <c r="C190" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/12/2026</t>
+          <t xml:space="preserve">14/12/2026</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F190" s="9">
@@ -21431,16 +21431,16 @@
         </is>
       </c>
       <c r="C191" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/12/2026</t>
+          <t xml:space="preserve">16/12/2026</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F191" s="9">
@@ -21459,16 +21459,16 @@
         </is>
       </c>
       <c r="C192" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/12/2026</t>
+          <t xml:space="preserve">21/12/2026</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F192" s="9">
@@ -21487,16 +21487,16 @@
         </is>
       </c>
       <c r="C193" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/12/2026</t>
+          <t xml:space="preserve">23/12/2026</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F193" s="9">
@@ -21515,16 +21515,16 @@
         </is>
       </c>
       <c r="C194" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/12/2026</t>
+          <t xml:space="preserve">28/12/2026</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F194" s="9">
@@ -21543,16 +21543,16 @@
         </is>
       </c>
       <c r="C195" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/01/2027</t>
+          <t xml:space="preserve">30/12/2026</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F195" s="9">
@@ -21571,16 +21571,16 @@
         </is>
       </c>
       <c r="C196" s="9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/01/2027</t>
+          <t xml:space="preserve">04/01/2027</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F196" s="9">
@@ -21599,16 +21599,16 @@
         </is>
       </c>
       <c r="C197" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/01/2027</t>
+          <t xml:space="preserve">08/01/2027</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F197" s="9">
@@ -21627,16 +21627,16 @@
         </is>
       </c>
       <c r="C198" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/01/2027</t>
+          <t xml:space="preserve">11/01/2027</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F198" s="9">
@@ -21655,16 +21655,16 @@
         </is>
       </c>
       <c r="C199" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/01/2027</t>
+          <t xml:space="preserve">13/01/2027</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F199" s="9">
@@ -21683,16 +21683,16 @@
         </is>
       </c>
       <c r="C200" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/01/2027</t>
+          <t xml:space="preserve">18/01/2027</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F200" s="9">
@@ -21711,16 +21711,16 @@
         </is>
       </c>
       <c r="C201" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/01/2027</t>
+          <t xml:space="preserve">20/01/2027</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F201" s="9">
@@ -21739,16 +21739,16 @@
         </is>
       </c>
       <c r="C202" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/01/2027</t>
+          <t xml:space="preserve">25/01/2027</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F202" s="9">
@@ -21767,16 +21767,16 @@
         </is>
       </c>
       <c r="C203" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/02/2027</t>
+          <t xml:space="preserve">27/01/2027</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F203" s="9">
@@ -21795,16 +21795,16 @@
         </is>
       </c>
       <c r="C204" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/02/2027</t>
+          <t xml:space="preserve">01/02/2027</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F204" s="9">
@@ -21823,16 +21823,16 @@
         </is>
       </c>
       <c r="C205" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/02/2027</t>
+          <t xml:space="preserve">03/02/2027</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F205" s="9">
@@ -21851,16 +21851,16 @@
         </is>
       </c>
       <c r="C206" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/02/2027</t>
+          <t xml:space="preserve">08/02/2027</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F206" s="9">
@@ -21879,16 +21879,16 @@
         </is>
       </c>
       <c r="C207" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/02/2027</t>
+          <t xml:space="preserve">10/02/2027</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F207" s="9">
@@ -21907,16 +21907,16 @@
         </is>
       </c>
       <c r="C208" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/02/2027</t>
+          <t xml:space="preserve">15/02/2027</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F208" s="9">
@@ -21935,16 +21935,16 @@
         </is>
       </c>
       <c r="C209" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/02/2027</t>
+          <t xml:space="preserve">17/02/2027</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F209" s="9">
@@ -21963,16 +21963,16 @@
         </is>
       </c>
       <c r="C210" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/02/2027</t>
+          <t xml:space="preserve">22/02/2027</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F210" s="9">
@@ -21991,16 +21991,16 @@
         </is>
       </c>
       <c r="C211" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/03/2027</t>
+          <t xml:space="preserve">24/02/2027</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F211" s="9">
@@ -22019,16 +22019,16 @@
         </is>
       </c>
       <c r="C212" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/03/2027</t>
+          <t xml:space="preserve">01/03/2027</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F212" s="9">
@@ -22047,16 +22047,16 @@
         </is>
       </c>
       <c r="C213" s="9">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/03/2027</t>
+          <t xml:space="preserve">03/03/2027</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F213" s="9">
@@ -22075,16 +22075,16 @@
         </is>
       </c>
       <c r="C214" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/03/2027</t>
+          <t xml:space="preserve">08/03/2027</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F214" s="9">
@@ -22103,16 +22103,16 @@
         </is>
       </c>
       <c r="C215" s="9">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/03/2027</t>
+          <t xml:space="preserve">10/03/2027</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F215" s="9">
@@ -22131,16 +22131,16 @@
         </is>
       </c>
       <c r="C216" s="9">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/03/2027</t>
+          <t xml:space="preserve">15/03/2027</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F216" s="9">
@@ -22159,16 +22159,16 @@
         </is>
       </c>
       <c r="C217" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/03/2027</t>
+          <t xml:space="preserve">17/03/2027</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F217" s="9">
@@ -22187,16 +22187,16 @@
         </is>
       </c>
       <c r="C218" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/03/2027</t>
+          <t xml:space="preserve">22/03/2027</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F218" s="9">
@@ -22215,11 +22215,11 @@
         </is>
       </c>
       <c r="C219" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31/03/2027</t>
+          <t xml:space="preserve">24/03/2027</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -22243,16 +22243,16 @@
         </is>
       </c>
       <c r="C220" s="9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/04/2027</t>
+          <t xml:space="preserve">31/03/2027</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F220" s="9">
@@ -22271,16 +22271,16 @@
         </is>
       </c>
       <c r="C221" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/04/2027</t>
+          <t xml:space="preserve">02/04/2027</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F221" s="9">
@@ -22299,16 +22299,16 @@
         </is>
       </c>
       <c r="C222" s="9">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/04/2027</t>
+          <t xml:space="preserve">05/04/2027</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F222" s="9">
@@ -22327,16 +22327,16 @@
         </is>
       </c>
       <c r="C223" s="9">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/04/2027</t>
+          <t xml:space="preserve">07/04/2027</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F223" s="9">
@@ -22355,16 +22355,16 @@
         </is>
       </c>
       <c r="C224" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/04/2027</t>
+          <t xml:space="preserve">12/04/2027</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F224" s="9">
@@ -22383,16 +22383,16 @@
         </is>
       </c>
       <c r="C225" s="9">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/04/2027</t>
+          <t xml:space="preserve">14/04/2027</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F225" s="9">
@@ -22411,16 +22411,16 @@
         </is>
       </c>
       <c r="C226" s="9">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/04/2027</t>
+          <t xml:space="preserve">19/04/2027</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F226" s="9">
@@ -22439,16 +22439,16 @@
         </is>
       </c>
       <c r="C227" s="9">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/04/2027</t>
+          <t xml:space="preserve">21/04/2027</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F227" s="9">
@@ -22467,16 +22467,16 @@
         </is>
       </c>
       <c r="C228" s="9">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/04/2027</t>
+          <t xml:space="preserve">26/04/2027</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F228" s="9">
@@ -22495,16 +22495,16 @@
         </is>
       </c>
       <c r="C229" s="9">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/05/2027</t>
+          <t xml:space="preserve">28/04/2027</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F229" s="9">
@@ -22523,16 +22523,16 @@
         </is>
       </c>
       <c r="C230" s="9">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/05/2027</t>
+          <t xml:space="preserve">03/05/2027</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F230" s="9">
@@ -22551,11 +22551,11 @@
         </is>
       </c>
       <c r="C231" s="9">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/05/2027</t>
+          <t xml:space="preserve">05/05/2027</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -22579,16 +22579,16 @@
         </is>
       </c>
       <c r="C232" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/05/2027</t>
+          <t xml:space="preserve">12/05/2027</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F232" s="9">
@@ -22607,16 +22607,16 @@
         </is>
       </c>
       <c r="C233" s="9">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/05/2027</t>
+          <t xml:space="preserve">14/05/2027</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F233" s="9">
@@ -22635,16 +22635,16 @@
         </is>
       </c>
       <c r="C234" s="9">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/05/2027</t>
+          <t xml:space="preserve">17/05/2027</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F234" s="9">
@@ -22663,16 +22663,16 @@
         </is>
       </c>
       <c r="C235" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/05/2027</t>
+          <t xml:space="preserve">19/05/2027</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F235" s="9">
@@ -22691,16 +22691,16 @@
         </is>
       </c>
       <c r="C236" s="9">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/05/2027</t>
+          <t xml:space="preserve">24/05/2027</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F236" s="9">
@@ -22719,16 +22719,16 @@
         </is>
       </c>
       <c r="C237" s="9">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31/05/2027</t>
+          <t xml:space="preserve">26/05/2027</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F237" s="9">
@@ -22747,16 +22747,16 @@
         </is>
       </c>
       <c r="C238" s="9">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/06/2027</t>
+          <t xml:space="preserve">31/05/2027</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F238" s="9">
@@ -22775,16 +22775,16 @@
         </is>
       </c>
       <c r="C239" s="9">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/06/2027</t>
+          <t xml:space="preserve">04/06/2027</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F239" s="9">
@@ -22803,16 +22803,16 @@
         </is>
       </c>
       <c r="C240" s="9">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/06/2027</t>
+          <t xml:space="preserve">07/06/2027</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F240" s="9">
@@ -22831,16 +22831,16 @@
         </is>
       </c>
       <c r="C241" s="9">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/06/2027</t>
+          <t xml:space="preserve">09/06/2027</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F241" s="9">
@@ -22859,16 +22859,16 @@
         </is>
       </c>
       <c r="C242" s="9">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/06/2027</t>
+          <t xml:space="preserve">14/06/2027</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F242" s="9">
@@ -22887,16 +22887,16 @@
         </is>
       </c>
       <c r="C243" s="9">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/06/2027</t>
+          <t xml:space="preserve">16/06/2027</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F243" s="9">
@@ -22915,16 +22915,16 @@
         </is>
       </c>
       <c r="C244" s="9">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/06/2027</t>
+          <t xml:space="preserve">21/06/2027</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F244" s="9">
@@ -22943,16 +22943,16 @@
         </is>
       </c>
       <c r="C245" s="9">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/06/2027</t>
+          <t xml:space="preserve">23/06/2027</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F245" s="9">
@@ -22971,16 +22971,16 @@
         </is>
       </c>
       <c r="C246" s="9">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/06/2027</t>
+          <t xml:space="preserve">28/06/2027</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F246" s="9">
@@ -22999,16 +22999,16 @@
         </is>
       </c>
       <c r="C247" s="9">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/07/2027</t>
+          <t xml:space="preserve">30/06/2027</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F247" s="9">
@@ -23027,16 +23027,16 @@
         </is>
       </c>
       <c r="C248" s="9">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/07/2027</t>
+          <t xml:space="preserve">05/07/2027</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F248" s="9">
@@ -23055,16 +23055,16 @@
         </is>
       </c>
       <c r="C249" s="9">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/07/2027</t>
+          <t xml:space="preserve">07/07/2027</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F249" s="9">
@@ -23083,16 +23083,16 @@
         </is>
       </c>
       <c r="C250" s="9">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/07/2027</t>
+          <t xml:space="preserve">12/07/2027</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F250" s="9">
@@ -23111,16 +23111,16 @@
         </is>
       </c>
       <c r="C251" s="9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/07/2027</t>
+          <t xml:space="preserve">14/07/2027</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F251" s="9">
@@ -23139,16 +23139,16 @@
         </is>
       </c>
       <c r="C252" s="9">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/07/2027</t>
+          <t xml:space="preserve">19/07/2027</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F252" s="9">
@@ -23167,16 +23167,16 @@
         </is>
       </c>
       <c r="C253" s="9">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/07/2027</t>
+          <t xml:space="preserve">21/07/2027</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F253" s="9">
@@ -23195,16 +23195,16 @@
         </is>
       </c>
       <c r="C254" s="9">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/07/2027</t>
+          <t xml:space="preserve">26/07/2027</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F254" s="9">
@@ -23223,16 +23223,16 @@
         </is>
       </c>
       <c r="C255" s="9">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/08/2027</t>
+          <t xml:space="preserve">28/07/2027</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F255" s="9">
@@ -23251,16 +23251,16 @@
         </is>
       </c>
       <c r="C256" s="9">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/08/2027</t>
+          <t xml:space="preserve">02/08/2027</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F256" s="9">
@@ -23279,16 +23279,16 @@
         </is>
       </c>
       <c r="C257" s="9">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/08/2027</t>
+          <t xml:space="preserve">04/08/2027</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F257" s="9">
@@ -23307,16 +23307,16 @@
         </is>
       </c>
       <c r="C258" s="9">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/08/2027</t>
+          <t xml:space="preserve">09/08/2027</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F258" s="9">
@@ -23335,16 +23335,16 @@
         </is>
       </c>
       <c r="C259" s="9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/08/2027</t>
+          <t xml:space="preserve">11/08/2027</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F259" s="9">
@@ -23363,16 +23363,16 @@
         </is>
       </c>
       <c r="C260" s="9">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/08/2027</t>
+          <t xml:space="preserve">16/08/2027</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F260" s="9">
@@ -23391,16 +23391,16 @@
         </is>
       </c>
       <c r="C261" s="9">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/08/2027</t>
+          <t xml:space="preserve">18/08/2027</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F261" s="9">
@@ -23419,16 +23419,16 @@
         </is>
       </c>
       <c r="C262" s="9">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/08/2027</t>
+          <t xml:space="preserve">23/08/2027</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercoledi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F262" s="9">
@@ -23447,20 +23447,20 @@
         </is>
       </c>
       <c r="C263" s="9">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/08/2027</t>
+          <t xml:space="preserve">25/08/2027</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F263" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -23471,20 +23471,20 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gigante</t>
+          <t xml:space="preserve">Amenduni</t>
         </is>
       </c>
       <c r="C264" s="9">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/09/2026</t>
+          <t xml:space="preserve">30/08/2027</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Lunedi</t>
         </is>
       </c>
       <c r="F264" s="9">
@@ -23503,20 +23503,20 @@
         </is>
       </c>
       <c r="C265" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/09/2026</t>
+          <t xml:space="preserve">01/09/2026</t>
         </is>
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F265" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -23531,16 +23531,16 @@
         </is>
       </c>
       <c r="C266" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/09/2026</t>
+          <t xml:space="preserve">09/09/2026</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F266" s="9">
@@ -23559,20 +23559,20 @@
         </is>
       </c>
       <c r="C267" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/09/2026</t>
+          <t xml:space="preserve">11/09/2026</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F267" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -23587,20 +23587,20 @@
         </is>
       </c>
       <c r="C268" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/09/2026</t>
+          <t xml:space="preserve">15/09/2026</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F268" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -23615,16 +23615,16 @@
         </is>
       </c>
       <c r="C269" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/09/2026</t>
+          <t xml:space="preserve">23/09/2026</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F269" s="9">
@@ -23643,20 +23643,20 @@
         </is>
       </c>
       <c r="C270" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/09/2026</t>
+          <t xml:space="preserve">25/09/2026</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F270" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -23671,20 +23671,20 @@
         </is>
       </c>
       <c r="C271" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/10/2026</t>
+          <t xml:space="preserve">29/09/2026</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F271" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -23699,16 +23699,16 @@
         </is>
       </c>
       <c r="C272" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/10/2026</t>
+          <t xml:space="preserve">07/10/2026</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F272" s="9">
@@ -23727,20 +23727,20 @@
         </is>
       </c>
       <c r="C273" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/10/2026</t>
+          <t xml:space="preserve">09/10/2026</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F273" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -23755,20 +23755,20 @@
         </is>
       </c>
       <c r="C274" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/10/2026</t>
+          <t xml:space="preserve">13/10/2026</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F274" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -23783,16 +23783,16 @@
         </is>
       </c>
       <c r="C275" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/10/2026</t>
+          <t xml:space="preserve">21/10/2026</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F275" s="9">
@@ -23811,20 +23811,20 @@
         </is>
       </c>
       <c r="C276" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/10/2026</t>
+          <t xml:space="preserve">23/10/2026</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F276" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -23839,20 +23839,20 @@
         </is>
       </c>
       <c r="C277" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/11/2026</t>
+          <t xml:space="preserve">27/10/2026</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F277" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -23867,16 +23867,16 @@
         </is>
       </c>
       <c r="C278" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">06/11/2026</t>
+          <t xml:space="preserve">04/11/2026</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F278" s="9">
@@ -23895,20 +23895,20 @@
         </is>
       </c>
       <c r="C279" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2026</t>
+          <t xml:space="preserve">06/11/2026</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F279" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -23923,20 +23923,20 @@
         </is>
       </c>
       <c r="C280" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/11/2026</t>
+          <t xml:space="preserve">10/11/2026</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F280" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -23951,16 +23951,16 @@
         </is>
       </c>
       <c r="C281" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/11/2026</t>
+          <t xml:space="preserve">18/11/2026</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F281" s="9">
@@ -23979,20 +23979,20 @@
         </is>
       </c>
       <c r="C282" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/11/2026</t>
+          <t xml:space="preserve">20/11/2026</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F282" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -24007,20 +24007,20 @@
         </is>
       </c>
       <c r="C283" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/11/2026</t>
+          <t xml:space="preserve">24/11/2026</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F283" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -24035,16 +24035,16 @@
         </is>
       </c>
       <c r="C284" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04/12/2026</t>
+          <t xml:space="preserve">02/12/2026</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F284" s="9">
@@ -24063,20 +24063,20 @@
         </is>
       </c>
       <c r="C285" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/12/2026</t>
+          <t xml:space="preserve">04/12/2026</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giovedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F285" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
@@ -24091,20 +24091,20 @@
         </is>
       </c>
       <c r="C286" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/12/2026</t>
+          <t xml:space="preserve">10/12/2026</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Giovedi</t>
         </is>
       </c>
       <c r="F286" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -24119,16 +24119,16 @@
         </is>
       </c>
       <c r="C287" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/12/2026</t>
+          <t xml:space="preserve">16/12/2026</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F287" s="9">
@@ -24147,20 +24147,20 @@
         </is>
       </c>
       <c r="C288" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/12/2026</t>
+          <t xml:space="preserve">18/12/2026</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F288" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -24175,16 +24175,16 @@
         </is>
       </c>
       <c r="C289" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/12/2026</t>
+          <t xml:space="preserve">22/12/2026</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F289" s="9">
@@ -24203,16 +24203,16 @@
         </is>
       </c>
       <c r="C290" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/01/2027</t>
+          <t xml:space="preserve">30/12/2026</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F290" s="9">
@@ -24231,20 +24231,20 @@
         </is>
       </c>
       <c r="C291" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/01/2027</t>
+          <t xml:space="preserve">05/01/2027</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F291" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -24259,16 +24259,16 @@
         </is>
       </c>
       <c r="C292" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/01/2027</t>
+          <t xml:space="preserve">13/01/2027</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F292" s="9">
@@ -24287,20 +24287,20 @@
         </is>
       </c>
       <c r="C293" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/01/2027</t>
+          <t xml:space="preserve">15/01/2027</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F293" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -24315,20 +24315,20 @@
         </is>
       </c>
       <c r="C294" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/01/2027</t>
+          <t xml:space="preserve">19/01/2027</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F294" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -24343,16 +24343,16 @@
         </is>
       </c>
       <c r="C295" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/01/2027</t>
+          <t xml:space="preserve">27/01/2027</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F295" s="9">
@@ -24371,20 +24371,20 @@
         </is>
       </c>
       <c r="C296" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/02/2027</t>
+          <t xml:space="preserve">29/01/2027</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F296" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -24399,20 +24399,20 @@
         </is>
       </c>
       <c r="C297" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/02/2027</t>
+          <t xml:space="preserve">02/02/2027</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F297" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -24427,16 +24427,16 @@
         </is>
       </c>
       <c r="C298" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/02/2027</t>
+          <t xml:space="preserve">10/02/2027</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F298" s="9">
@@ -24455,20 +24455,20 @@
         </is>
       </c>
       <c r="C299" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/02/2027</t>
+          <t xml:space="preserve">12/02/2027</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F299" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -24483,20 +24483,20 @@
         </is>
       </c>
       <c r="C300" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/02/2027</t>
+          <t xml:space="preserve">16/02/2027</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F300" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -24511,16 +24511,16 @@
         </is>
       </c>
       <c r="C301" s="9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/02/2027</t>
+          <t xml:space="preserve">24/02/2027</t>
         </is>
       </c>
       <c r="E301" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F301" s="9">
@@ -24539,20 +24539,20 @@
         </is>
       </c>
       <c r="C302" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/03/2027</t>
+          <t xml:space="preserve">26/02/2027</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F302" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -24567,20 +24567,20 @@
         </is>
       </c>
       <c r="C303" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08/03/2027</t>
+          <t xml:space="preserve">02/03/2027</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F303" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -24595,16 +24595,16 @@
         </is>
       </c>
       <c r="C304" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/03/2027</t>
+          <t xml:space="preserve">10/03/2027</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F304" s="9">
@@ -24623,20 +24623,20 @@
         </is>
       </c>
       <c r="C305" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/03/2027</t>
+          <t xml:space="preserve">12/03/2027</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F305" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -24651,20 +24651,20 @@
         </is>
       </c>
       <c r="C306" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/03/2027</t>
+          <t xml:space="preserve">16/03/2027</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F306" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -24679,16 +24679,16 @@
         </is>
       </c>
       <c r="C307" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/03/2027</t>
+          <t xml:space="preserve">24/03/2027</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F307" s="9">
@@ -24707,20 +24707,20 @@
         </is>
       </c>
       <c r="C308" s="9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/03/2027</t>
+          <t xml:space="preserve">26/03/2027</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F308" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
@@ -24735,20 +24735,20 @@
         </is>
       </c>
       <c r="C309" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/04/2027</t>
+          <t xml:space="preserve">30/03/2027</t>
         </is>
       </c>
       <c r="E309" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F309" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -24763,16 +24763,16 @@
         </is>
       </c>
       <c r="C310" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/04/2027</t>
+          <t xml:space="preserve">07/04/2027</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F310" s="9">
@@ -24791,20 +24791,20 @@
         </is>
       </c>
       <c r="C311" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13/04/2027</t>
+          <t xml:space="preserve">09/04/2027</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F311" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -24819,20 +24819,20 @@
         </is>
       </c>
       <c r="C312" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">19/04/2027</t>
+          <t xml:space="preserve">13/04/2027</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F312" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -24847,16 +24847,16 @@
         </is>
       </c>
       <c r="C313" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/04/2027</t>
+          <t xml:space="preserve">21/04/2027</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F313" s="9">
@@ -24875,20 +24875,20 @@
         </is>
       </c>
       <c r="C314" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/04/2027</t>
+          <t xml:space="preserve">23/04/2027</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F314" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -24903,20 +24903,20 @@
         </is>
       </c>
       <c r="C315" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">03/05/2027</t>
+          <t xml:space="preserve">27/04/2027</t>
         </is>
       </c>
       <c r="E315" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F315" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -24931,16 +24931,16 @@
         </is>
       </c>
       <c r="C316" s="9">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">07/05/2027</t>
+          <t xml:space="preserve">05/05/2027</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F316" s="9">
@@ -24959,20 +24959,20 @@
         </is>
       </c>
       <c r="C317" s="9">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/05/2027</t>
+          <t xml:space="preserve">07/05/2027</t>
         </is>
       </c>
       <c r="E317" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F317" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -24987,20 +24987,20 @@
         </is>
       </c>
       <c r="C318" s="9">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/05/2027</t>
+          <t xml:space="preserve">11/05/2027</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F318" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -25015,16 +25015,16 @@
         </is>
       </c>
       <c r="C319" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/05/2027</t>
+          <t xml:space="preserve">19/05/2027</t>
         </is>
       </c>
       <c r="E319" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venerdi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F319" s="9">
@@ -25043,20 +25043,20 @@
         </is>
       </c>
       <c r="C320" s="9">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/05/2027</t>
+          <t xml:space="preserve">21/05/2027</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martedi</t>
+          <t xml:space="preserve">Venerdi</t>
         </is>
       </c>
       <c r="F320" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -25071,16 +25071,16 @@
         </is>
       </c>
       <c r="C321" s="9">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31/05/2027</t>
+          <t xml:space="preserve">25/05/2027</t>
         </is>
       </c>
       <c r="E321" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Martedi</t>
         </is>
       </c>
       <c r="F321" s="9">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="C322" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
@@ -25127,16 +25127,16 @@
         </is>
       </c>
       <c r="C323" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/06/2027</t>
+          <t xml:space="preserve">16/06/2027</t>
         </is>
       </c>
       <c r="E323" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F323" s="9">
@@ -25155,7 +25155,7 @@
         </is>
       </c>
       <c r="C324" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         </is>
       </c>
       <c r="C325" s="9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
@@ -25211,16 +25211,16 @@
         </is>
       </c>
       <c r="C326" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28/06/2027</t>
+          <t xml:space="preserve">30/06/2027</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F326" s="9">
@@ -25239,7 +25239,7 @@
         </is>
       </c>
       <c r="C327" s="9">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="C328" s="9">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
@@ -25295,16 +25295,16 @@
         </is>
       </c>
       <c r="C329" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/07/2027</t>
+          <t xml:space="preserve">14/07/2027</t>
         </is>
       </c>
       <c r="E329" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F329" s="9">
@@ -25323,7 +25323,7 @@
         </is>
       </c>
       <c r="C330" s="9">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="C331" s="9">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
@@ -25379,16 +25379,16 @@
         </is>
       </c>
       <c r="C332" s="9">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/07/2027</t>
+          <t xml:space="preserve">28/07/2027</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F332" s="9">
@@ -25407,7 +25407,7 @@
         </is>
       </c>
       <c r="C333" s="9">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="C334" s="9">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
@@ -25463,16 +25463,16 @@
         </is>
       </c>
       <c r="C335" s="9">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">09/08/2027</t>
+          <t xml:space="preserve">11/08/2027</t>
         </is>
       </c>
       <c r="E335" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F335" s="9">
@@ -25491,7 +25491,7 @@
         </is>
       </c>
       <c r="C336" s="9">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         </is>
       </c>
       <c r="C337" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
@@ -25547,16 +25547,16 @@
         </is>
       </c>
       <c r="C338" s="9">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/08/2027</t>
+          <t xml:space="preserve">25/08/2027</t>
         </is>
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunedi</t>
+          <t xml:space="preserve">Mercoledi</t>
         </is>
       </c>
       <c r="F338" s="9">
@@ -25575,7 +25575,7 @@
         </is>
       </c>
       <c r="C339" s="9">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         </is>
       </c>
       <c r="C340" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
@@ -36829,8 +36829,8 @@
       <c r="B43" s="9">
         <v>4</v>
       </c>
-      <c r="C43" s="11">
-        <v>1</v>
+      <c r="C43" s="9">
+        <v>2</v>
       </c>
       <c r="D43" s="9">
         <v>1</v>
@@ -36839,7 +36839,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="9">
         <v>1</v>
@@ -37390,7 +37390,7 @@
         <v>254</v>
       </c>
       <c r="C57" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57" s="9">
         <v>79</v>
@@ -37399,7 +37399,7 @@
         <v>105</v>
       </c>
       <c r="F57" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G57" s="9">
         <v>52</v>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 31/05/2027: Caforio ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi)</t>
+          <t xml:space="preserve">Settimana del 31/05/2027: Gigante ha svolto 0 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi)</t>
         </is>
       </c>
     </row>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 31/05/2027: Gigante ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi)</t>
+          <t xml:space="preserve">Settimana del 30/08/2027: Amenduni ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
         </is>
       </c>
     </row>
@@ -37513,7 +37513,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 30/08/2027: Amenduni ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
+          <t xml:space="preserve">Settimana del 30/08/2027: Caforio ha svolto 0 turno/i invece di 1 (giorno/i non lavorativo/i: Giovedi)</t>
         </is>
       </c>
     </row>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 30/08/2027: Caforio ha svolto 0 turno/i invece di 1 (giorno/i non lavorativo/i: Giovedi)</t>
+          <t xml:space="preserve">Settimana del 30/08/2027: Donnaloia ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
         </is>
       </c>
     </row>
@@ -37533,7 +37533,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 30/08/2027: Donnaloia ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
+          <t xml:space="preserve">Settimana del 30/08/2027: Prota ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
         </is>
       </c>
     </row>
@@ -37543,7 +37543,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 30/08/2027: Prota ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
+          <t xml:space="preserve">Settimana del 30/08/2027: Raffaele ha svolto 0 turno/i invece di 1 (giorno/i non lavorativo/i: Giovedi)</t>
         </is>
       </c>
     </row>
@@ -37553,22 +37553,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settimana del 30/08/2027: Raffaele ha svolto 0 turno/i invece di 1 (giorno/i non lavorativo/i: Giovedi)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9">
-        <v>11</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
           <t xml:space="preserve">Settimana del 30/08/2027: Scalone ha svolto 1 turno/i invece di 2 (giorno/i non lavorativo/i: Mercoledi, Venerdi)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -37581,7 +37571,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -37651,7 +37640,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caforio: alterna 1/2 turni; mai Lunedi ne' Martedi (2 turni = Mer+Ven, 1 turno = Gio).</t>
+          <t xml:space="preserve">Caforio: alterna 1/2 turni; turni solo Lun/Gio/Ven (2 turni = Lun+Ven, 1 turno = Gio).</t>
         </is>
       </c>
     </row>
